--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611256</v>
+        <v>122611339</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R2" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>57389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,12 +822,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611339</v>
+        <v>122611313</v>
       </c>
       <c r="B4" t="n">
-        <v>57534</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,16 +940,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>578083</v>
       </c>
       <c r="R4" t="n">
-        <v>6430968</v>
+        <v>6430858</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611286</v>
+        <v>122611256</v>
       </c>
       <c r="B5" t="n">
-        <v>57389</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1033,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611339</v>
+        <v>122611286</v>
       </c>
       <c r="B2" t="n">
-        <v>57534</v>
+        <v>57389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,10 +714,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R2" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611286</v>
+        <v>122611302</v>
       </c>
       <c r="B3" t="n">
-        <v>57389</v>
+        <v>57534</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +832,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R3" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611313</v>
+        <v>122611339</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>57534</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,12 +940,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578083</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>6430858</v>
+        <v>6430968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611302</v>
+        <v>122611313</v>
       </c>
       <c r="B6" t="n">
-        <v>57534</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,16 +1168,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611286</v>
+        <v>122611313</v>
       </c>
       <c r="B2" t="n">
-        <v>57389</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R2" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -907,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B4" t="n">
-        <v>57534</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,33 +915,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -959,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R4" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611256</v>
+        <v>122611286</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,33 +1029,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1135,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611313</v>
+        <v>122611339</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>57534</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,20 +1143,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,12 +1164,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578083</v>
+        <v>577901</v>
       </c>
       <c r="R6" t="n">
-        <v>6430858</v>
+        <v>6430968</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R2" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611302</v>
+        <v>122611256</v>
       </c>
       <c r="B3" t="n">
-        <v>57534</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,26 +809,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -837,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611256</v>
+        <v>122611339</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57535</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +923,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611286</v>
+        <v>122611313</v>
       </c>
       <c r="B5" t="n">
-        <v>57389</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,20 +1054,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R5" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611339</v>
+        <v>122611302</v>
       </c>
       <c r="B6" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577901</v>
+        <v>578083</v>
       </c>
       <c r="R6" t="n">
-        <v>6430968</v>
+        <v>6430858</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,6 +1243,349 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122691281</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>578009</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6431084</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122691332</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57535</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577922</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6431022</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122691196</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57537</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578013</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6431084</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611286</v>
+        <v>122611256</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611256</v>
+        <v>122611302</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57535</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -845,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R3" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1021,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1029,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,12 +1050,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R5" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611302</v>
+        <v>122611313</v>
       </c>
       <c r="B6" t="n">
-        <v>57535</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,16 +1168,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611256</v>
+        <v>122611302</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R2" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611302</v>
+        <v>122611286</v>
       </c>
       <c r="B3" t="n">
-        <v>57535</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,10 +828,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B4" t="n">
-        <v>57535</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,33 +923,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R4" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611286</v>
+        <v>122611339</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57535</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,14 +1060,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R5" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611302</v>
+        <v>122611286</v>
       </c>
       <c r="B2" t="n">
-        <v>57535</v>
+        <v>57484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,10 +714,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R2" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611286</v>
+        <v>122611313</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +805,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,20 +826,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R3" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611256</v>
+        <v>122611339</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,33 +919,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -959,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611339</v>
+        <v>122611302</v>
       </c>
       <c r="B5" t="n">
-        <v>57535</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577901</v>
+        <v>578083</v>
       </c>
       <c r="R5" t="n">
-        <v>6430968</v>
+        <v>6430858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611313</v>
+        <v>122611256</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,33 +1143,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R6" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691281</v>
+        <v>122691196</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578009</v>
+        <v>578013</v>
       </c>
       <c r="R7" t="n">
         <v>6431084</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691332</v>
+        <v>122691281</v>
       </c>
       <c r="B8" t="n">
-        <v>57535</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,39 +1371,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1412,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577922</v>
+        <v>578009</v>
       </c>
       <c r="R8" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,6 +1455,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691196</v>
+        <v>122691332</v>
       </c>
       <c r="B9" t="n">
-        <v>57537</v>
+        <v>57629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,26 +1490,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578013</v>
+        <v>577922</v>
       </c>
       <c r="R9" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1362,7 +1362,7 @@
         <v>122691281</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,33 +919,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R4" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611302</v>
+        <v>122611339</v>
       </c>
       <c r="B5" t="n">
         <v>57629</v>
@@ -1059,7 +1059,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578083</v>
+        <v>577901</v>
       </c>
       <c r="R5" t="n">
-        <v>6430858</v>
+        <v>6430968</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611256</v>
+        <v>122611302</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,26 +1147,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R6" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611286</v>
+        <v>122611339</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,14 +714,10 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R2" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,12 +822,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611256</v>
+        <v>122611302</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,26 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -955,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R4" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,33 +1037,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R5" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611302</v>
+        <v>122611313</v>
       </c>
       <c r="B6" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,16 +1168,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691196</v>
+        <v>122691281</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578013</v>
+        <v>578009</v>
       </c>
       <c r="R7" t="n">
         <v>6431084</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691281</v>
+        <v>122691332</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>57629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,39 +1372,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578009</v>
+        <v>577922</v>
       </c>
       <c r="R8" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1456,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691332</v>
+        <v>122691196</v>
       </c>
       <c r="B9" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,26 +1490,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577922</v>
+        <v>578013</v>
       </c>
       <c r="R9" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B2" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R2" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611286</v>
+        <v>122611302</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +828,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R3" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611302</v>
+        <v>122611313</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,16 +936,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1021,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611256</v>
+        <v>122611339</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,33 +1029,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R5" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,20 +1139,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,12 +1160,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R6" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691281</v>
+        <v>122691332</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>57629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578009</v>
+        <v>577922</v>
       </c>
       <c r="R7" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691332</v>
+        <v>122691196</v>
       </c>
       <c r="B8" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1375,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577922</v>
+        <v>578013</v>
       </c>
       <c r="R8" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691196</v>
+        <v>122691281</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,39 +1485,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1526,13 +1525,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578013</v>
+        <v>578009</v>
       </c>
       <c r="R9" t="n">
         <v>6431084</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1569,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611256</v>
+        <v>122611339</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R2" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611302</v>
+        <v>122611256</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R3" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611313</v>
+        <v>122611286</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,12 +936,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R4" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611339</v>
+        <v>122611313</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,16 +1054,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1065,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577901</v>
+        <v>578083</v>
       </c>
       <c r="R5" t="n">
-        <v>6430968</v>
+        <v>6430858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611286</v>
+        <v>122611302</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,16 +1147,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1166,14 +1170,10 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R6" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691332</v>
+        <v>122691281</v>
       </c>
       <c r="B7" t="n">
-        <v>57629</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577922</v>
+        <v>578009</v>
       </c>
       <c r="R7" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1473,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691281</v>
+        <v>122691332</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>57629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1486,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1525,13 +1526,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578009</v>
+        <v>577922</v>
       </c>
       <c r="R9" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1570,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611256</v>
+        <v>122611286</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,33 +805,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611286</v>
+        <v>122611302</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,14 +946,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R4" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611313</v>
+        <v>122611256</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,33 +1033,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1069,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578083</v>
+        <v>578034</v>
       </c>
       <c r="R5" t="n">
-        <v>6430858</v>
+        <v>6430863</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611302</v>
+        <v>122611313</v>
       </c>
       <c r="B6" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,20 +1147,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,16 +1168,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691281</v>
+        <v>122691196</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578009</v>
+        <v>578013</v>
       </c>
       <c r="R7" t="n">
         <v>6431084</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1341,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691196</v>
+        <v>122691332</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,26 +1375,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1412,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578013</v>
+        <v>577922</v>
       </c>
       <c r="R8" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691332</v>
+        <v>122691281</v>
       </c>
       <c r="B9" t="n">
-        <v>57629</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,39 +1485,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1526,13 +1525,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577922</v>
+        <v>578009</v>
       </c>
       <c r="R9" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,6 +1569,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611339</v>
+        <v>122611256</v>
       </c>
       <c r="B2" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R2" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611302</v>
+        <v>122611339</v>
       </c>
       <c r="B4" t="n">
         <v>57629</v>
@@ -949,7 +949,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578083</v>
+        <v>577901</v>
       </c>
       <c r="R4" t="n">
-        <v>6430858</v>
+        <v>6430968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611256</v>
+        <v>122611302</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,26 +1037,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578034</v>
+        <v>578083</v>
       </c>
       <c r="R5" t="n">
-        <v>6430863</v>
+        <v>6430858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691196</v>
+        <v>122691281</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,39 +1257,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578013</v>
+        <v>578009</v>
       </c>
       <c r="R7" t="n">
         <v>6431084</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691332</v>
+        <v>122691196</v>
       </c>
       <c r="B8" t="n">
-        <v>57629</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,26 +1376,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1411,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577922</v>
+        <v>578013</v>
       </c>
       <c r="R8" t="n">
-        <v>6431022</v>
+        <v>6431084</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1473,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691281</v>
+        <v>122691332</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,39 +1486,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1525,13 +1526,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578009</v>
+        <v>577922</v>
       </c>
       <c r="R9" t="n">
-        <v>6431084</v>
+        <v>6431022</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1570,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1586,6 +1586,1058 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124753795</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578034</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6430863</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124753705</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578003</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6430982</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124753768</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577977</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6430917</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124753863</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577901</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6430968</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124753730</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577959</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6431070</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124782120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>578016</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6430925</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124777640</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577892</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6430782</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124778736</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577964</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6431049</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124778411</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577990</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6431082</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753795</v>
+        <v>124753705</v>
       </c>
       <c r="B10" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578034</v>
+        <v>578003</v>
       </c>
       <c r="R10" t="n">
-        <v>6430863</v>
+        <v>6430982</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,6 +1676,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753705</v>
+        <v>124753795</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1719,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578003</v>
+        <v>578034</v>
       </c>
       <c r="R11" t="n">
-        <v>6430982</v>
+        <v>6430863</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,11 +1795,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753768</v>
+        <v>124753863</v>
       </c>
       <c r="B12" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,21 +1837,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577977</v>
+        <v>577901</v>
       </c>
       <c r="R12" t="n">
-        <v>6430917</v>
+        <v>6430968</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753863</v>
+        <v>124753768</v>
       </c>
       <c r="B13" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577901</v>
+        <v>577977</v>
       </c>
       <c r="R13" t="n">
-        <v>6430968</v>
+        <v>6430917</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2201,24 +2201,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R15" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,9 +2245,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,19 +2272,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2317,7 +2324,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R16" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778736</v>
+        <v>124782120</v>
       </c>
       <c r="B17" t="n">
         <v>57519</v>
@@ -2436,21 +2443,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577964</v>
+        <v>578016</v>
       </c>
       <c r="R17" t="n">
-        <v>6431049</v>
+        <v>6430925</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2480,19 +2490,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778411</v>
+        <v>124777640</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577990</v>
+        <v>577892</v>
       </c>
       <c r="R18" t="n">
-        <v>6431082</v>
+        <v>6430782</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753705</v>
+        <v>124753768</v>
       </c>
       <c r="B10" t="n">
         <v>57519</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578003</v>
+        <v>577977</v>
       </c>
       <c r="R10" t="n">
-        <v>6430982</v>
+        <v>6430917</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,11 +1676,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753795</v>
+        <v>124753705</v>
       </c>
       <c r="B11" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578034</v>
+        <v>578003</v>
       </c>
       <c r="R11" t="n">
-        <v>6430863</v>
+        <v>6430982</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1795,6 +1790,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B12" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R12" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753768</v>
+        <v>124753863</v>
       </c>
       <c r="B13" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577977</v>
+        <v>577901</v>
       </c>
       <c r="R13" t="n">
-        <v>6430917</v>
+        <v>6430968</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778411</v>
+        <v>124778736</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577990</v>
+        <v>577964</v>
       </c>
       <c r="R15" t="n">
-        <v>6431082</v>
+        <v>6431049</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778736</v>
+        <v>124782120</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2322,21 +2322,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577964</v>
+        <v>578016</v>
       </c>
       <c r="R16" t="n">
-        <v>6431049</v>
+        <v>6430925</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2366,19 +2369,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,22 +2386,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B17" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,21 +2414,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2443,24 +2436,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R17" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,9 +2480,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,12 +2507,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B10" t="n">
         <v>57519</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R10" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753705</v>
+        <v>124753795</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578003</v>
+        <v>578034</v>
       </c>
       <c r="R11" t="n">
-        <v>6430982</v>
+        <v>6430863</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753795</v>
+        <v>124753768</v>
       </c>
       <c r="B12" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,25 +1828,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578034</v>
+        <v>577977</v>
       </c>
       <c r="R12" t="n">
-        <v>6430863</v>
+        <v>6430917</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2049,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753730</v>
+        <v>124753705</v>
       </c>
       <c r="B14" t="n">
         <v>57519</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577959</v>
+        <v>578003</v>
       </c>
       <c r="R14" t="n">
-        <v>6431070</v>
+        <v>6430982</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,6 +2132,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778736</v>
+        <v>124778411</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577964</v>
+        <v>577990</v>
       </c>
       <c r="R15" t="n">
-        <v>6431049</v>
+        <v>6431082</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124782120</v>
+        <v>124778736</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2322,24 +2322,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578016</v>
+        <v>577964</v>
       </c>
       <c r="R16" t="n">
-        <v>6430925</v>
+        <v>6431049</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,9 +2366,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,22 +2393,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778411</v>
+        <v>124777640</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,21 +2421,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2438,7 +2445,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577990</v>
+        <v>577892</v>
       </c>
       <c r="R17" t="n">
-        <v>6431082</v>
+        <v>6430782</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2519,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124777640</v>
+        <v>124782120</v>
       </c>
       <c r="B18" t="n">
         <v>57519</v>
@@ -2557,21 +2564,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577892</v>
+        <v>578016</v>
       </c>
       <c r="R18" t="n">
-        <v>6430782</v>
+        <v>6430925</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2601,19 +2611,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753795</v>
+        <v>124753863</v>
       </c>
       <c r="B11" t="n">
-        <v>56821</v>
+        <v>57761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100038</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R11" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B12" t="n">
         <v>57519</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R12" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,6 +1904,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B13" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,25 +1947,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R13" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2044,7 +2049,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753705</v>
+        <v>124753768</v>
       </c>
       <c r="B14" t="n">
         <v>57519</v>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578003</v>
+        <v>577977</v>
       </c>
       <c r="R14" t="n">
-        <v>6430982</v>
+        <v>6430917</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,11 +2137,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778411</v>
+        <v>124782120</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2201,21 +2201,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577990</v>
+        <v>578016</v>
       </c>
       <c r="R15" t="n">
-        <v>6431082</v>
+        <v>6430925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,19 +2248,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,12 +2265,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2526,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,24 +2557,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R18" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2611,9 +2601,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753730</v>
+        <v>124753863</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577959</v>
+        <v>577901</v>
       </c>
       <c r="R10" t="n">
-        <v>6431070</v>
+        <v>6430968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B11" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R11" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753705</v>
+        <v>124753768</v>
       </c>
       <c r="B12" t="n">
         <v>57519</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578003</v>
+        <v>577977</v>
       </c>
       <c r="R12" t="n">
-        <v>6430982</v>
+        <v>6430917</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,11 +1904,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753795</v>
+        <v>124753730</v>
       </c>
       <c r="B13" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,25 +1942,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578034</v>
+        <v>577959</v>
       </c>
       <c r="R13" t="n">
-        <v>6430863</v>
+        <v>6431070</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B14" t="n">
         <v>57519</v>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R14" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,6 +2132,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R10" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753795</v>
+        <v>124753863</v>
       </c>
       <c r="B11" t="n">
-        <v>56821</v>
+        <v>57761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100038</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R11" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B12" t="n">
         <v>57519</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R12" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,6 +1904,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,7 +2049,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753705</v>
+        <v>124753768</v>
       </c>
       <c r="B14" t="n">
         <v>57519</v>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578003</v>
+        <v>577977</v>
       </c>
       <c r="R14" t="n">
-        <v>6430982</v>
+        <v>6430917</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,11 +2137,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2277,7 +2277,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778736</v>
+        <v>124777640</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577964</v>
+        <v>577892</v>
       </c>
       <c r="R16" t="n">
-        <v>6431049</v>
+        <v>6430782</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B17" t="n">
         <v>57519</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R17" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753795</v>
+        <v>124753863</v>
       </c>
       <c r="B10" t="n">
-        <v>56821</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578034</v>
+        <v>577901</v>
       </c>
       <c r="R10" t="n">
-        <v>6430863</v>
+        <v>6430968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753863</v>
+        <v>124753768</v>
       </c>
       <c r="B11" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577901</v>
+        <v>577977</v>
       </c>
       <c r="R11" t="n">
-        <v>6430968</v>
+        <v>6430917</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753730</v>
+        <v>124753795</v>
       </c>
       <c r="B13" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577959</v>
+        <v>578034</v>
       </c>
       <c r="R13" t="n">
-        <v>6431070</v>
+        <v>6430863</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B14" t="n">
         <v>57519</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R14" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124782120</v>
+        <v>124777640</v>
       </c>
       <c r="B15" t="n">
         <v>57519</v>
@@ -2201,24 +2201,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578016</v>
+        <v>577892</v>
       </c>
       <c r="R15" t="n">
-        <v>6430925</v>
+        <v>6430782</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,9 +2245,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,19 +2272,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2317,7 +2324,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R16" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778736</v>
+        <v>124778411</v>
       </c>
       <c r="B17" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,21 +2421,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2438,7 +2445,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577964</v>
+        <v>577990</v>
       </c>
       <c r="R17" t="n">
-        <v>6431049</v>
+        <v>6431082</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778411</v>
+        <v>124782120</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2557,21 +2564,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577990</v>
+        <v>578016</v>
       </c>
       <c r="R18" t="n">
-        <v>6431082</v>
+        <v>6430925</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2601,19 +2611,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R10" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753705</v>
+        <v>124753730</v>
       </c>
       <c r="B12" t="n">
         <v>57519</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578003</v>
+        <v>577959</v>
       </c>
       <c r="R12" t="n">
-        <v>6430982</v>
+        <v>6431070</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,11 +1904,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753795</v>
+        <v>124753705</v>
       </c>
       <c r="B13" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,25 +1942,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578034</v>
+        <v>578003</v>
       </c>
       <c r="R13" t="n">
-        <v>6430863</v>
+        <v>6430982</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2023,6 +2018,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753730</v>
+        <v>124753863</v>
       </c>
       <c r="B14" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577959</v>
+        <v>577901</v>
       </c>
       <c r="R14" t="n">
-        <v>6431070</v>
+        <v>6430968</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124777640</v>
+        <v>124782120</v>
       </c>
       <c r="B15" t="n">
         <v>57519</v>
@@ -2201,21 +2201,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577892</v>
+        <v>578016</v>
       </c>
       <c r="R15" t="n">
-        <v>6430782</v>
+        <v>6430925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,19 +2248,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2265,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778736</v>
+        <v>124778411</v>
       </c>
       <c r="B16" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,21 +2293,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2324,7 +2317,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2333,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577964</v>
+        <v>577990</v>
       </c>
       <c r="R16" t="n">
-        <v>6431049</v>
+        <v>6431082</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2368,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778411</v>
+        <v>124777640</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,21 +2414,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2445,7 +2438,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2454,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577990</v>
+        <v>577892</v>
       </c>
       <c r="R17" t="n">
-        <v>6431082</v>
+        <v>6430782</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2526,7 +2519,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124782120</v>
+        <v>124778736</v>
       </c>
       <c r="B18" t="n">
         <v>57519</v>
@@ -2564,24 +2557,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578016</v>
+        <v>577964</v>
       </c>
       <c r="R18" t="n">
-        <v>6430925</v>
+        <v>6431049</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2611,9 +2601,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753795</v>
+        <v>124753768</v>
       </c>
       <c r="B10" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578034</v>
+        <v>577977</v>
       </c>
       <c r="R10" t="n">
-        <v>6430863</v>
+        <v>6430917</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B11" t="n">
         <v>57519</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R11" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,6 +1790,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753730</v>
+        <v>124753795</v>
       </c>
       <c r="B12" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1868,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577959</v>
+        <v>578034</v>
       </c>
       <c r="R12" t="n">
-        <v>6431070</v>
+        <v>6430863</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753705</v>
+        <v>124753730</v>
       </c>
       <c r="B13" t="n">
         <v>57519</v>
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578003</v>
+        <v>577959</v>
       </c>
       <c r="R13" t="n">
-        <v>6430982</v>
+        <v>6431070</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2018,11 +2023,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2277,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778411</v>
+        <v>124777640</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577990</v>
+        <v>577892</v>
       </c>
       <c r="R16" t="n">
-        <v>6431082</v>
+        <v>6430782</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B17" t="n">
         <v>57519</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R17" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778736</v>
+        <v>124778411</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577964</v>
+        <v>577990</v>
       </c>
       <c r="R18" t="n">
-        <v>6431049</v>
+        <v>6431082</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B10" t="n">
         <v>57519</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R10" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753705</v>
+        <v>124753863</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578003</v>
+        <v>577901</v>
       </c>
       <c r="R11" t="n">
-        <v>6430982</v>
+        <v>6430968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,7 +1930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753730</v>
+        <v>124753768</v>
       </c>
       <c r="B13" t="n">
         <v>57519</v>
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577959</v>
+        <v>577977</v>
       </c>
       <c r="R13" t="n">
-        <v>6431070</v>
+        <v>6430917</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753863</v>
+        <v>124753705</v>
       </c>
       <c r="B14" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,21 +2060,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577901</v>
+        <v>578003</v>
       </c>
       <c r="R14" t="n">
-        <v>6430968</v>
+        <v>6430982</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,6 +2132,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2201,24 +2201,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R15" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,9 +2245,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,12 +2272,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2398,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778736</v>
+        <v>124782120</v>
       </c>
       <c r="B17" t="n">
         <v>57519</v>
@@ -2436,21 +2443,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577964</v>
+        <v>578016</v>
       </c>
       <c r="R17" t="n">
-        <v>6431049</v>
+        <v>6430925</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2480,19 +2490,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778411</v>
+        <v>124778736</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577990</v>
+        <v>577964</v>
       </c>
       <c r="R18" t="n">
-        <v>6431082</v>
+        <v>6431049</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753730</v>
+        <v>124753863</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577959</v>
+        <v>577901</v>
       </c>
       <c r="R10" t="n">
-        <v>6431070</v>
+        <v>6430968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753863</v>
+        <v>124753705</v>
       </c>
       <c r="B11" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577901</v>
+        <v>578003</v>
       </c>
       <c r="R11" t="n">
-        <v>6430968</v>
+        <v>6430982</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,6 +1790,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753795</v>
+        <v>124753768</v>
       </c>
       <c r="B12" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1868,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578034</v>
+        <v>577977</v>
       </c>
       <c r="R12" t="n">
-        <v>6430863</v>
+        <v>6430917</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,7 +1935,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B13" t="n">
         <v>57519</v>
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R13" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2044,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753705</v>
+        <v>124753795</v>
       </c>
       <c r="B14" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578003</v>
+        <v>578034</v>
       </c>
       <c r="R14" t="n">
-        <v>6430982</v>
+        <v>6430863</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,11 +2137,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778411</v>
+        <v>124778736</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577990</v>
+        <v>577964</v>
       </c>
       <c r="R15" t="n">
-        <v>6431082</v>
+        <v>6431049</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2519,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778736</v>
+        <v>124778411</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577964</v>
+        <v>577990</v>
       </c>
       <c r="R18" t="n">
-        <v>6431049</v>
+        <v>6431082</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753705</v>
+        <v>124753768</v>
       </c>
       <c r="B11" t="n">
         <v>57519</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578003</v>
+        <v>577977</v>
       </c>
       <c r="R11" t="n">
-        <v>6430982</v>
+        <v>6430917</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1790,11 +1790,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B12" t="n">
         <v>57519</v>
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R12" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,6 +1904,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2163,7 +2163,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778736</v>
+        <v>124782120</v>
       </c>
       <c r="B15" t="n">
         <v>57519</v>
@@ -2201,21 +2201,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577964</v>
+        <v>578016</v>
       </c>
       <c r="R15" t="n">
-        <v>6431049</v>
+        <v>6430925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,19 +2248,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,19 +2265,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2324,7 +2317,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2333,10 +2326,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R16" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2368,7 +2361,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2378,7 +2371,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B17" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,21 +2414,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2443,24 +2436,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R17" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,9 +2480,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778411</v>
+        <v>124777640</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577990</v>
+        <v>577892</v>
       </c>
       <c r="R18" t="n">
-        <v>6431082</v>
+        <v>6430782</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753863</v>
+        <v>124753795</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577901</v>
+        <v>578034</v>
       </c>
       <c r="R10" t="n">
-        <v>6430968</v>
+        <v>6430863</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B11" t="n">
         <v>57519</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R11" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753705</v>
+        <v>124753863</v>
       </c>
       <c r="B12" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578003</v>
+        <v>577901</v>
       </c>
       <c r="R12" t="n">
-        <v>6430982</v>
+        <v>6430968</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,11 +1904,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753730</v>
+        <v>124753705</v>
       </c>
       <c r="B13" t="n">
         <v>57519</v>
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577959</v>
+        <v>578003</v>
       </c>
       <c r="R13" t="n">
-        <v>6431070</v>
+        <v>6430982</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2023,6 +2018,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753795</v>
+        <v>124753768</v>
       </c>
       <c r="B14" t="n">
-        <v>56821</v>
+        <v>57519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578034</v>
+        <v>577977</v>
       </c>
       <c r="R14" t="n">
-        <v>6430863</v>
+        <v>6430917</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B15" t="n">
-        <v>57519</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2201,24 +2201,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R15" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,9 +2245,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,19 +2272,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778736</v>
+        <v>124777640</v>
       </c>
       <c r="B16" t="n">
         <v>57519</v>
@@ -2317,7 +2324,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2326,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577964</v>
+        <v>577892</v>
       </c>
       <c r="R16" t="n">
-        <v>6431049</v>
+        <v>6430782</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,7 +2368,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2371,7 +2378,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778411</v>
+        <v>124778736</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,21 +2421,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2438,7 +2445,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577990</v>
+        <v>577964</v>
       </c>
       <c r="R17" t="n">
-        <v>6431082</v>
+        <v>6431049</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,7 +2526,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124777640</v>
+        <v>124782120</v>
       </c>
       <c r="B18" t="n">
         <v>57519</v>
@@ -2557,21 +2564,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577892</v>
+        <v>578016</v>
       </c>
       <c r="R18" t="n">
-        <v>6430782</v>
+        <v>6430925</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2601,19 +2611,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1591,7 +1591,7 @@
         <v>124753795</v>
       </c>
       <c r="B10" t="n">
-        <v>56821</v>
+        <v>56939</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753730</v>
+        <v>124753768</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577959</v>
+        <v>577977</v>
       </c>
       <c r="R11" t="n">
-        <v>6431070</v>
+        <v>6430917</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753863</v>
+        <v>124753730</v>
       </c>
       <c r="B12" t="n">
-        <v>57761</v>
+        <v>57648</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577901</v>
+        <v>577959</v>
       </c>
       <c r="R12" t="n">
-        <v>6430968</v>
+        <v>6431070</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753705</v>
+        <v>124753863</v>
       </c>
       <c r="B13" t="n">
-        <v>57519</v>
+        <v>57914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578003</v>
+        <v>577901</v>
       </c>
       <c r="R13" t="n">
-        <v>6430982</v>
+        <v>6430968</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2018,11 +2018,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753768</v>
+        <v>124753705</v>
       </c>
       <c r="B14" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577977</v>
+        <v>578003</v>
       </c>
       <c r="R14" t="n">
-        <v>6430917</v>
+        <v>6430982</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,6 +2132,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,7 +2166,7 @@
         <v>124778411</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124777640</v>
+        <v>124782120</v>
       </c>
       <c r="B16" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,21 +2322,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577892</v>
+        <v>578016</v>
       </c>
       <c r="R16" t="n">
-        <v>6430782</v>
+        <v>6430925</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2366,19 +2369,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,22 +2386,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778736</v>
+        <v>124777640</v>
       </c>
       <c r="B17" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,7 +2438,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2454,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577964</v>
+        <v>577892</v>
       </c>
       <c r="R17" t="n">
-        <v>6431049</v>
+        <v>6430782</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124782120</v>
+        <v>124778736</v>
       </c>
       <c r="B18" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,24 +2557,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578016</v>
+        <v>577964</v>
       </c>
       <c r="R18" t="n">
-        <v>6430925</v>
+        <v>6431049</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2611,9 +2601,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753795</v>
+        <v>124753705</v>
       </c>
       <c r="B10" t="n">
-        <v>56939</v>
+        <v>57648</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578034</v>
+        <v>578003</v>
       </c>
       <c r="R10" t="n">
-        <v>6430863</v>
+        <v>6430982</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,6 +1676,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753768</v>
+        <v>124753730</v>
       </c>
       <c r="B11" t="n">
         <v>57648</v>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577977</v>
+        <v>577959</v>
       </c>
       <c r="R11" t="n">
-        <v>6430917</v>
+        <v>6431070</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1816,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753730</v>
+        <v>124753768</v>
       </c>
       <c r="B12" t="n">
         <v>57648</v>
@@ -1868,10 +1873,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577959</v>
+        <v>577977</v>
       </c>
       <c r="R12" t="n">
-        <v>6431070</v>
+        <v>6430917</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2044,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753705</v>
+        <v>124753795</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>56939</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578003</v>
+        <v>578034</v>
       </c>
       <c r="R14" t="n">
-        <v>6430982</v>
+        <v>6430863</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,11 +2137,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124778411</v>
+        <v>124782120</v>
       </c>
       <c r="B15" t="n">
-        <v>57793</v>
+        <v>57648</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2201,21 +2201,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577990</v>
+        <v>578016</v>
       </c>
       <c r="R15" t="n">
-        <v>6431082</v>
+        <v>6430925</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,19 +2248,9 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2265,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124782120</v>
+        <v>124778411</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,21 +2293,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2322,24 +2315,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578016</v>
+        <v>577990</v>
       </c>
       <c r="R16" t="n">
-        <v>6430925</v>
+        <v>6431082</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,9 +2359,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,19 +2386,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124777640</v>
+        <v>124778736</v>
       </c>
       <c r="B17" t="n">
         <v>57648</v>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577892</v>
+        <v>577964</v>
       </c>
       <c r="R17" t="n">
-        <v>6430782</v>
+        <v>6431049</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,7 +2519,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124778736</v>
+        <v>124777640</v>
       </c>
       <c r="B18" t="n">
         <v>57648</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577964</v>
+        <v>577892</v>
       </c>
       <c r="R18" t="n">
-        <v>6431049</v>
+        <v>6430782</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4397-2025 artfynd.xlsx
+++ b/artfynd/A 4397-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122611256</v>
+        <v>124753795</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,12 +787,7 @@
         <v>122611286</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611339</v>
+        <v>124753705</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577901</v>
+        <v>578003</v>
       </c>
       <c r="R4" t="n">
-        <v>6430968</v>
+        <v>6430982</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611302</v>
+        <v>124753730</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,16 +1022,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,7 +1048,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578083</v>
+        <v>577959</v>
       </c>
       <c r="R5" t="n">
-        <v>6430858</v>
+        <v>6431070</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,32 +1120,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611313</v>
+        <v>124753768</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,12 +1148,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1183,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578083</v>
+        <v>577977</v>
       </c>
       <c r="R6" t="n">
-        <v>6430858</v>
+        <v>6430917</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,65 +1229,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122691281</v>
+        <v>124777640</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578009</v>
+        <v>577892</v>
       </c>
       <c r="R7" t="n">
-        <v>6431084</v>
+        <v>6430782</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,12 +1303,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,34 +1327,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122691196</v>
+        <v>124778736</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,46 +1356,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 4397, St Överström, Sm</t>
+          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578013</v>
+        <v>577964</v>
       </c>
       <c r="R8" t="n">
-        <v>6431084</v>
+        <v>6431049</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,12 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,27 +1449,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122691332</v>
+        <v>124782120</v>
       </c>
       <c r="B9" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,16 +1472,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1516,7 +1498,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1526,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577922</v>
+        <v>578016</v>
       </c>
       <c r="R9" t="n">
-        <v>6431022</v>
+        <v>6430925</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1556,12 +1538,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1563,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124753705</v>
+        <v>124753863</v>
       </c>
       <c r="B10" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,21 +1581,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578003</v>
+        <v>577901</v>
       </c>
       <c r="R10" t="n">
-        <v>6430982</v>
+        <v>6430968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,11 +1653,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Trummade flitigt från flera platser, men mest från död gammal asp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,32 +1679,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124753730</v>
+        <v>122611313</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1740,16 +1707,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1759,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577959</v>
+        <v>578083</v>
       </c>
       <c r="R11" t="n">
-        <v>6431070</v>
+        <v>6430858</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,12 +1752,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,15 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124753768</v>
+        <v>122611302</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,16 +1795,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1863,7 +1821,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1873,10 +1831,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577977</v>
+        <v>578083</v>
       </c>
       <c r="R12" t="n">
-        <v>6430917</v>
+        <v>6430858</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,12 +1861,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,15 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124753863</v>
+        <v>122611339</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,21 +1904,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2017,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,37 +2002,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124753795</v>
+        <v>122691332</v>
       </c>
       <c r="B14" t="n">
-        <v>56939</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>103020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2091,7 +2039,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2101,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578034</v>
+        <v>577922</v>
       </c>
       <c r="R14" t="n">
-        <v>6430863</v>
+        <v>6431022</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2131,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,15 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124782120</v>
+        <v>124753832</v>
       </c>
       <c r="B15" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,16 +2122,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2215,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578016</v>
+        <v>577782</v>
       </c>
       <c r="R15" t="n">
-        <v>6430925</v>
+        <v>6430917</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,22 +2213,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124778411</v>
+        <v>122611256</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,24 +2250,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577990</v>
+        <v>578034</v>
       </c>
       <c r="R16" t="n">
-        <v>6431082</v>
+        <v>6430863</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2356,22 +2297,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,27 +2317,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124778736</v>
+        <v>122691196</v>
       </c>
       <c r="B17" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,43 +2340,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stora Överström a4397, Stora Överström a4397, Sm</t>
+          <t>A 4397, St Överström, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577964</v>
+        <v>578013</v>
       </c>
       <c r="R17" t="n">
-        <v>6431049</v>
+        <v>6431084</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2477,22 +2406,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,27 +2426,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124777640</v>
+        <v>124778411</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,21 +2449,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2559,7 +2473,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577892</v>
+        <v>577990</v>
       </c>
       <c r="R18" t="n">
-        <v>6430782</v>
+        <v>6431082</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2637,6 +2551,116 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122691281</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 4397, St Överström, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>578009</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6431084</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
